--- a/backend/src/modules/contracts/templates/suit-agency-contract.xlsx
+++ b/backend/src/modules/contracts/templates/suit-agency-contract.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c5f20152e993edc/AICRM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nurier/Library/CloudStorage/OneDrive-개인/AICRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B02836EB-1C5A-2748-923D-9E3999C8883F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6624D276-DCBE-6143-A31B-CEB467AC97B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="720" windowWidth="35740" windowHeight="26220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">계약서!$B$2:$AY$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -597,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -650,77 +649,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -733,6 +688,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -742,15 +700,55 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -983,14 +981,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>120160</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>187569</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>7814</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>16608</xdr:rowOff>
+      <xdr:rowOff>36146</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1013,7 +1011,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="120160" y="9321800"/>
+          <a:off x="120160" y="9341338"/>
           <a:ext cx="571500" cy="571500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1367,30 +1365,30 @@
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="30" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="30" t="s">
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="30" t="s">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
       <c r="X2" s="10"/>
@@ -1427,42 +1425,42 @@
     </row>
     <row r="4" spans="2:50" ht="27" customHeight="1">
       <c r="B4" s="11"/>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="Q4" s="51" t="s">
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="Q4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
       <c r="AX4" s="12"/>
     </row>
     <row r="5" spans="2:50" ht="10.75" customHeight="1">
@@ -1471,124 +1469,124 @@
     </row>
     <row r="6" spans="2:50" ht="22" customHeight="1">
       <c r="B6" s="11"/>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="41" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="42"/>
-      <c r="AH6" s="42"/>
-      <c r="AI6" s="42"/>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="42"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="42"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="42"/>
-      <c r="AQ6" s="42"/>
-      <c r="AR6" s="42"/>
-      <c r="AS6" s="42"/>
-      <c r="AT6" s="42"/>
-      <c r="AU6" s="42"/>
-      <c r="AV6" s="42"/>
-      <c r="AW6" s="42"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="64"/>
+      <c r="AH6" s="64"/>
+      <c r="AI6" s="64"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
+      <c r="AL6" s="64"/>
+      <c r="AM6" s="64"/>
+      <c r="AN6" s="64"/>
+      <c r="AO6" s="64"/>
+      <c r="AP6" s="64"/>
+      <c r="AQ6" s="64"/>
+      <c r="AR6" s="64"/>
+      <c r="AS6" s="64"/>
+      <c r="AT6" s="64"/>
+      <c r="AU6" s="64"/>
+      <c r="AV6" s="64"/>
+      <c r="AW6" s="64"/>
       <c r="AX6" s="18"/>
     </row>
     <row r="7" spans="2:50" ht="24.25" customHeight="1">
       <c r="B7" s="11"/>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="50" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="31" t="s">
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="31" t="s">
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="58" t="s">
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="AB7" s="35"/>
-      <c r="AC7" s="35"/>
-      <c r="AD7" s="35"/>
-      <c r="AE7" s="35"/>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="50" t="s">
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="38"/>
-      <c r="AK7" s="38"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="31" t="s">
+      <c r="AH7" s="35"/>
+      <c r="AI7" s="35"/>
+      <c r="AJ7" s="35"/>
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="35"/>
+      <c r="AM7" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="AN7" s="38"/>
-      <c r="AO7" s="38"/>
-      <c r="AP7" s="38"/>
-      <c r="AQ7" s="38"/>
-      <c r="AR7" s="38"/>
-      <c r="AS7" s="31" t="s">
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="35"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="35"/>
+      <c r="AS7" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="32"/>
+      <c r="AT7" s="34"/>
+      <c r="AU7" s="34"/>
+      <c r="AV7" s="34"/>
+      <c r="AW7" s="61"/>
       <c r="AX7" s="12"/>
     </row>
     <row r="8" spans="2:50" ht="7.25" customHeight="1">
@@ -1597,17 +1595,17 @@
     </row>
     <row r="9" spans="2:50" ht="8" customHeight="1">
       <c r="B9" s="11"/>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -1650,15 +1648,15 @@
     </row>
     <row r="10" spans="2:50" ht="10.5" customHeight="1">
       <c r="B10" s="11"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
       <c r="AH10" s="13" t="s">
         <v>10</v>
       </c>
@@ -1679,15 +1677,15 @@
     </row>
     <row r="11" spans="2:50" ht="10.5" customHeight="1">
       <c r="B11" s="11"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
       <c r="AH11" s="13" t="s">
         <v>11</v>
       </c>
@@ -1708,15 +1706,15 @@
     </row>
     <row r="12" spans="2:50" ht="10.5" customHeight="1">
       <c r="B12" s="11"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
       <c r="AH12" s="13" t="s">
         <v>12</v>
       </c>
@@ -1798,124 +1796,124 @@
     </row>
     <row r="16" spans="2:50" ht="15.75" customHeight="1">
       <c r="B16" s="11"/>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="39" t="s">
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="56"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="56"/>
+      <c r="Z16" s="56"/>
+      <c r="AA16" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="39"/>
-      <c r="AE16" s="39"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="64"/>
-      <c r="AH16" s="26" t="s">
+      <c r="AB16" s="47"/>
+      <c r="AC16" s="47"/>
+      <c r="AD16" s="47"/>
+      <c r="AE16" s="47"/>
+      <c r="AF16" s="47"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="AI16" s="26"/>
-      <c r="AJ16" s="26"/>
-      <c r="AK16" s="26"/>
-      <c r="AL16" s="65"/>
-      <c r="AM16" s="26" t="s">
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="46"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="27"/>
+      <c r="AM16" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="AN16" s="26"/>
-      <c r="AO16" s="26"/>
-      <c r="AP16" s="26"/>
-      <c r="AQ16" s="26"/>
-      <c r="AR16" s="26"/>
-      <c r="AS16" s="26" t="s">
+      <c r="AN16" s="46"/>
+      <c r="AO16" s="46"/>
+      <c r="AP16" s="46"/>
+      <c r="AQ16" s="46"/>
+      <c r="AR16" s="46"/>
+      <c r="AS16" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="AT16" s="26"/>
-      <c r="AU16" s="26"/>
-      <c r="AV16" s="26"/>
-      <c r="AW16" s="27"/>
+      <c r="AT16" s="46"/>
+      <c r="AU16" s="46"/>
+      <c r="AV16" s="46"/>
+      <c r="AW16" s="58"/>
       <c r="AX16" s="19"/>
     </row>
     <row r="17" spans="2:50" ht="17.5" customHeight="1">
       <c r="B17" s="11"/>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="39" t="s">
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="56"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="56"/>
+      <c r="U17" s="56"/>
+      <c r="V17" s="56"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="56"/>
+      <c r="Z17" s="56"/>
+      <c r="AA17" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="39"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="39"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="48" t="s">
+      <c r="AB17" s="47"/>
+      <c r="AC17" s="47"/>
+      <c r="AD17" s="47"/>
+      <c r="AE17" s="47"/>
+      <c r="AF17" s="47"/>
+      <c r="AG17" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="AH17" s="40"/>
-      <c r="AI17" s="40"/>
-      <c r="AJ17" s="40"/>
-      <c r="AK17" s="40"/>
-      <c r="AL17" s="40"/>
-      <c r="AM17" s="26" t="s">
+      <c r="AH17" s="55"/>
+      <c r="AI17" s="55"/>
+      <c r="AJ17" s="55"/>
+      <c r="AK17" s="55"/>
+      <c r="AL17" s="55"/>
+      <c r="AM17" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="AN17" s="40"/>
-      <c r="AO17" s="40"/>
-      <c r="AP17" s="40"/>
-      <c r="AQ17" s="40"/>
-      <c r="AR17" s="40"/>
-      <c r="AS17" s="26" t="s">
+      <c r="AN17" s="55"/>
+      <c r="AO17" s="55"/>
+      <c r="AP17" s="55"/>
+      <c r="AQ17" s="55"/>
+      <c r="AR17" s="55"/>
+      <c r="AS17" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="AT17" s="26"/>
-      <c r="AU17" s="26"/>
-      <c r="AV17" s="26"/>
-      <c r="AW17" s="27"/>
+      <c r="AT17" s="46"/>
+      <c r="AU17" s="46"/>
+      <c r="AV17" s="46"/>
+      <c r="AW17" s="58"/>
       <c r="AX17" s="12"/>
     </row>
     <row r="18" spans="2:50" ht="7.25" customHeight="1">
@@ -1924,162 +1922,162 @@
     </row>
     <row r="19" spans="2:50" ht="11" customHeight="1">
       <c r="B19" s="11"/>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="44"/>
-      <c r="AE19" s="44"/>
-      <c r="AF19" s="44"/>
-      <c r="AG19" s="44"/>
-      <c r="AH19" s="44"/>
-      <c r="AI19" s="44"/>
-      <c r="AJ19" s="44"/>
-      <c r="AK19" s="44"/>
-      <c r="AL19" s="44"/>
-      <c r="AM19" s="44"/>
-      <c r="AN19" s="44"/>
-      <c r="AO19" s="44"/>
-      <c r="AP19" s="44"/>
-      <c r="AQ19" s="44"/>
-      <c r="AR19" s="44"/>
-      <c r="AS19" s="44"/>
-      <c r="AT19" s="44"/>
-      <c r="AU19" s="44"/>
-      <c r="AV19" s="44"/>
-      <c r="AW19" s="44"/>
-      <c r="AX19" s="45"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="50"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="50"/>
+      <c r="Y19" s="50"/>
+      <c r="Z19" s="50"/>
+      <c r="AA19" s="50"/>
+      <c r="AB19" s="50"/>
+      <c r="AC19" s="50"/>
+      <c r="AD19" s="50"/>
+      <c r="AE19" s="50"/>
+      <c r="AF19" s="50"/>
+      <c r="AG19" s="50"/>
+      <c r="AH19" s="50"/>
+      <c r="AI19" s="50"/>
+      <c r="AJ19" s="50"/>
+      <c r="AK19" s="50"/>
+      <c r="AL19" s="50"/>
+      <c r="AM19" s="50"/>
+      <c r="AN19" s="50"/>
+      <c r="AO19" s="50"/>
+      <c r="AP19" s="50"/>
+      <c r="AQ19" s="50"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
+      <c r="AT19" s="50"/>
+      <c r="AU19" s="50"/>
+      <c r="AV19" s="50"/>
+      <c r="AW19" s="50"/>
+      <c r="AX19" s="51"/>
     </row>
     <row r="20" spans="2:50" ht="11" customHeight="1">
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="60"/>
-      <c r="Q20" s="60"/>
-      <c r="R20" s="60"/>
-      <c r="S20" s="60"/>
-      <c r="T20" s="60"/>
-      <c r="U20" s="60"/>
-      <c r="V20" s="60"/>
-      <c r="W20" s="60"/>
-      <c r="X20" s="60"/>
-      <c r="Y20" s="60"/>
-      <c r="Z20" s="60"/>
-      <c r="AA20" s="60"/>
-      <c r="AB20" s="60"/>
-      <c r="AC20" s="60"/>
-      <c r="AD20" s="60"/>
-      <c r="AE20" s="60"/>
-      <c r="AF20" s="60"/>
-      <c r="AG20" s="60"/>
-      <c r="AH20" s="60"/>
-      <c r="AI20" s="60"/>
-      <c r="AJ20" s="60"/>
-      <c r="AK20" s="60"/>
-      <c r="AL20" s="60"/>
-      <c r="AM20" s="60"/>
-      <c r="AN20" s="60"/>
-      <c r="AO20" s="60"/>
-      <c r="AP20" s="60"/>
-      <c r="AQ20" s="60"/>
-      <c r="AR20" s="60"/>
-      <c r="AS20" s="60"/>
-      <c r="AT20" s="60"/>
-      <c r="AU20" s="60"/>
-      <c r="AV20" s="60"/>
-      <c r="AW20" s="60"/>
-      <c r="AX20" s="61"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="43"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="43"/>
+      <c r="Z20" s="43"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="43"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="43"/>
+      <c r="AF20" s="43"/>
+      <c r="AG20" s="43"/>
+      <c r="AH20" s="43"/>
+      <c r="AI20" s="43"/>
+      <c r="AJ20" s="43"/>
+      <c r="AK20" s="43"/>
+      <c r="AL20" s="43"/>
+      <c r="AM20" s="43"/>
+      <c r="AN20" s="43"/>
+      <c r="AO20" s="43"/>
+      <c r="AP20" s="43"/>
+      <c r="AQ20" s="43"/>
+      <c r="AR20" s="43"/>
+      <c r="AS20" s="43"/>
+      <c r="AT20" s="43"/>
+      <c r="AU20" s="43"/>
+      <c r="AV20" s="43"/>
+      <c r="AW20" s="43"/>
+      <c r="AX20" s="44"/>
     </row>
     <row r="21" spans="2:50" ht="11" customHeight="1">
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="60"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="60"/>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="60"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="60"/>
-      <c r="AE21" s="60"/>
-      <c r="AF21" s="60"/>
-      <c r="AG21" s="60"/>
-      <c r="AH21" s="60"/>
-      <c r="AI21" s="60"/>
-      <c r="AJ21" s="60"/>
-      <c r="AK21" s="60"/>
-      <c r="AL21" s="60"/>
-      <c r="AM21" s="60"/>
-      <c r="AN21" s="60"/>
-      <c r="AO21" s="60"/>
-      <c r="AP21" s="60"/>
-      <c r="AQ21" s="60"/>
-      <c r="AR21" s="60"/>
-      <c r="AS21" s="60"/>
-      <c r="AT21" s="60"/>
-      <c r="AU21" s="60"/>
-      <c r="AV21" s="60"/>
-      <c r="AW21" s="60"/>
-      <c r="AX21" s="61"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43"/>
+      <c r="V21" s="43"/>
+      <c r="W21" s="43"/>
+      <c r="X21" s="43"/>
+      <c r="Y21" s="43"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="43"/>
+      <c r="AD21" s="43"/>
+      <c r="AE21" s="43"/>
+      <c r="AF21" s="43"/>
+      <c r="AG21" s="43"/>
+      <c r="AH21" s="43"/>
+      <c r="AI21" s="43"/>
+      <c r="AJ21" s="43"/>
+      <c r="AK21" s="43"/>
+      <c r="AL21" s="43"/>
+      <c r="AM21" s="43"/>
+      <c r="AN21" s="43"/>
+      <c r="AO21" s="43"/>
+      <c r="AP21" s="43"/>
+      <c r="AQ21" s="43"/>
+      <c r="AR21" s="43"/>
+      <c r="AS21" s="43"/>
+      <c r="AT21" s="43"/>
+      <c r="AU21" s="43"/>
+      <c r="AV21" s="43"/>
+      <c r="AW21" s="43"/>
+      <c r="AX21" s="44"/>
     </row>
     <row r="22" spans="2:50" ht="6.75" customHeight="1">
       <c r="B22" s="11"/>
@@ -2087,18 +2085,18 @@
     </row>
     <row r="23" spans="2:50" ht="12.25" customHeight="1">
       <c r="B23" s="11"/>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
       <c r="AX23" s="12"/>
     </row>
     <row r="24" spans="2:50" ht="3.75" customHeight="1">
@@ -2266,23 +2264,23 @@
     </row>
     <row r="43" spans="2:50" ht="13.5" customHeight="1">
       <c r="B43" s="11"/>
-      <c r="C43" s="49" t="s">
+      <c r="C43" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="49"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
       <c r="AX43" s="12"/>
     </row>
     <row r="44" spans="2:50" ht="2.5" customHeight="1">
@@ -2309,43 +2307,40 @@
     </row>
     <row r="48" spans="2:50" ht="17" customHeight="1">
       <c r="B48" s="11"/>
-      <c r="K48" s="33" t="s">
+      <c r="K48" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="L48" s="34"/>
-      <c r="M48" s="34"/>
-      <c r="N48" s="34"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="34"/>
-      <c r="S48" s="34"/>
-      <c r="T48" s="34"/>
-      <c r="U48" s="34"/>
-      <c r="V48" s="34"/>
-      <c r="W48" s="34"/>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="33" t="s">
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
+      <c r="W48" s="29"/>
+      <c r="X48" s="29"/>
+      <c r="Y48" s="29"/>
+      <c r="Z48" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="AA48" s="33"/>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
-      <c r="AG48" s="62"/>
-      <c r="AH48" s="62"/>
-      <c r="AI48" s="62"/>
-      <c r="AM48" s="33" t="s">
+      <c r="AA48" s="28"/>
+      <c r="AB48" s="28"/>
+      <c r="AC48" s="28"/>
+      <c r="AD48" s="28"/>
+      <c r="AE48" s="28"/>
+      <c r="AF48" s="28"/>
+      <c r="AM48" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="AN48" s="34"/>
-      <c r="AO48" s="34"/>
-      <c r="AP48" s="34"/>
-      <c r="AQ48" s="34"/>
-      <c r="AR48" s="34"/>
+      <c r="AN48" s="29"/>
+      <c r="AO48" s="29"/>
+      <c r="AP48" s="29"/>
+      <c r="AQ48" s="29"/>
+      <c r="AR48" s="29"/>
       <c r="AX48" s="12"/>
     </row>
     <row r="49" spans="2:50" ht="9.5" customHeight="1">
@@ -2354,43 +2349,40 @@
     </row>
     <row r="50" spans="2:50" ht="17" customHeight="1">
       <c r="B50" s="11"/>
-      <c r="K50" s="33" t="s">
+      <c r="K50" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="S50" s="34"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="34"/>
-      <c r="X50" s="34"/>
-      <c r="Y50" s="34"/>
-      <c r="Z50" s="63" t="s">
+      <c r="L50" s="29"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
+      <c r="S50" s="29"/>
+      <c r="T50" s="29"/>
+      <c r="U50" s="29"/>
+      <c r="V50" s="29"/>
+      <c r="W50" s="29"/>
+      <c r="X50" s="29"/>
+      <c r="Y50" s="29"/>
+      <c r="Z50" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="AA50" s="63"/>
-      <c r="AB50" s="63"/>
-      <c r="AC50" s="63"/>
-      <c r="AD50" s="63"/>
-      <c r="AE50" s="63"/>
-      <c r="AF50" s="63"/>
-      <c r="AG50" s="62"/>
-      <c r="AH50" s="62"/>
-      <c r="AI50" s="62"/>
-      <c r="AM50" s="33" t="s">
+      <c r="AA50" s="45"/>
+      <c r="AB50" s="45"/>
+      <c r="AC50" s="45"/>
+      <c r="AD50" s="45"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AM50" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="AN50" s="34"/>
-      <c r="AO50" s="34"/>
-      <c r="AP50" s="34"/>
-      <c r="AQ50" s="34"/>
-      <c r="AR50" s="34"/>
+      <c r="AN50" s="29"/>
+      <c r="AO50" s="29"/>
+      <c r="AP50" s="29"/>
+      <c r="AQ50" s="29"/>
+      <c r="AR50" s="29"/>
       <c r="AX50" s="12"/>
     </row>
     <row r="51" spans="2:50" ht="9.5" customHeight="1">
@@ -2399,55 +2391,55 @@
     </row>
     <row r="52" spans="2:50" ht="14.75" customHeight="1">
       <c r="B52" s="11"/>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
-      <c r="Z52" s="28"/>
-      <c r="AA52" s="28"/>
-      <c r="AB52" s="28"/>
-      <c r="AC52" s="28"/>
-      <c r="AD52" s="28"/>
-      <c r="AE52" s="28"/>
-      <c r="AF52" s="28"/>
-      <c r="AG52" s="28"/>
-      <c r="AH52" s="28"/>
-      <c r="AI52" s="28"/>
-      <c r="AJ52" s="28"/>
-      <c r="AK52" s="28"/>
-      <c r="AL52" s="28"/>
-      <c r="AM52" s="28"/>
-      <c r="AN52" s="28"/>
-      <c r="AO52" s="28"/>
-      <c r="AP52" s="28"/>
-      <c r="AQ52" s="28"/>
-      <c r="AR52" s="28"/>
-      <c r="AS52" s="28"/>
-      <c r="AT52" s="28"/>
-      <c r="AU52" s="28"/>
-      <c r="AV52" s="28"/>
-      <c r="AW52" s="28"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="59"/>
+      <c r="R52" s="59"/>
+      <c r="S52" s="59"/>
+      <c r="T52" s="59"/>
+      <c r="U52" s="59"/>
+      <c r="V52" s="59"/>
+      <c r="W52" s="59"/>
+      <c r="X52" s="59"/>
+      <c r="Y52" s="59"/>
+      <c r="Z52" s="59"/>
+      <c r="AA52" s="59"/>
+      <c r="AB52" s="59"/>
+      <c r="AC52" s="59"/>
+      <c r="AD52" s="59"/>
+      <c r="AE52" s="59"/>
+      <c r="AF52" s="59"/>
+      <c r="AG52" s="59"/>
+      <c r="AH52" s="59"/>
+      <c r="AI52" s="59"/>
+      <c r="AJ52" s="59"/>
+      <c r="AK52" s="59"/>
+      <c r="AL52" s="59"/>
+      <c r="AM52" s="59"/>
+      <c r="AN52" s="59"/>
+      <c r="AO52" s="59"/>
+      <c r="AP52" s="59"/>
+      <c r="AQ52" s="59"/>
+      <c r="AR52" s="59"/>
+      <c r="AS52" s="59"/>
+      <c r="AT52" s="59"/>
+      <c r="AU52" s="59"/>
+      <c r="AV52" s="59"/>
+      <c r="AW52" s="59"/>
       <c r="AX52" s="12"/>
     </row>
     <row r="53" spans="2:50" ht="14" customHeight="1">
@@ -2555,49 +2547,49 @@
     <row r="57" spans="2:50" ht="22" customHeight="1" thickBot="1">
       <c r="D57" s="23"/>
       <c r="E57" s="23"/>
-      <c r="F57" s="29" t="s">
+      <c r="F57" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
-      <c r="R57" s="29"/>
-      <c r="S57" s="29"/>
-      <c r="T57" s="29"/>
-      <c r="U57" s="29"/>
-      <c r="V57" s="29"/>
-      <c r="W57" s="29"/>
-      <c r="X57" s="29"/>
-      <c r="Y57" s="29"/>
-      <c r="Z57" s="29"/>
-      <c r="AA57" s="29"/>
-      <c r="AB57" s="29"/>
-      <c r="AC57" s="29"/>
-      <c r="AD57" s="29"/>
-      <c r="AE57" s="29"/>
-      <c r="AF57" s="29"/>
-      <c r="AG57" s="29"/>
-      <c r="AH57" s="29"/>
-      <c r="AI57" s="29"/>
-      <c r="AJ57" s="29"/>
-      <c r="AK57" s="29"/>
-      <c r="AL57" s="29"/>
-      <c r="AM57" s="29"/>
-      <c r="AN57" s="29"/>
-      <c r="AO57" s="29"/>
-      <c r="AP57" s="29"/>
-      <c r="AQ57" s="29"/>
-      <c r="AR57" s="29"/>
-      <c r="AS57" s="29"/>
-      <c r="AT57" s="29"/>
+      <c r="G57" s="60"/>
+      <c r="H57" s="60"/>
+      <c r="I57" s="60"/>
+      <c r="J57" s="60"/>
+      <c r="K57" s="60"/>
+      <c r="L57" s="60"/>
+      <c r="M57" s="60"/>
+      <c r="N57" s="60"/>
+      <c r="O57" s="60"/>
+      <c r="P57" s="60"/>
+      <c r="Q57" s="60"/>
+      <c r="R57" s="60"/>
+      <c r="S57" s="60"/>
+      <c r="T57" s="60"/>
+      <c r="U57" s="60"/>
+      <c r="V57" s="60"/>
+      <c r="W57" s="60"/>
+      <c r="X57" s="60"/>
+      <c r="Y57" s="60"/>
+      <c r="Z57" s="60"/>
+      <c r="AA57" s="60"/>
+      <c r="AB57" s="60"/>
+      <c r="AC57" s="60"/>
+      <c r="AD57" s="60"/>
+      <c r="AE57" s="60"/>
+      <c r="AF57" s="60"/>
+      <c r="AG57" s="60"/>
+      <c r="AH57" s="60"/>
+      <c r="AI57" s="60"/>
+      <c r="AJ57" s="60"/>
+      <c r="AK57" s="60"/>
+      <c r="AL57" s="60"/>
+      <c r="AM57" s="60"/>
+      <c r="AN57" s="60"/>
+      <c r="AO57" s="60"/>
+      <c r="AP57" s="60"/>
+      <c r="AQ57" s="60"/>
+      <c r="AR57" s="60"/>
+      <c r="AS57" s="60"/>
+      <c r="AT57" s="60"/>
       <c r="AU57" s="21"/>
       <c r="AV57" s="21"/>
       <c r="AW57" s="21"/>
@@ -2608,6 +2600,33 @@
     <sortCondition sortBy="icon" ref="C55"/>
   </sortState>
   <mergeCells count="43">
+    <mergeCell ref="C52:AW52"/>
+    <mergeCell ref="F57:AT57"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="AS7:AW7"/>
+    <mergeCell ref="AS16:AW16"/>
+    <mergeCell ref="AM48:AR48"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="I16:Z16"/>
+    <mergeCell ref="I6:AC6"/>
+    <mergeCell ref="K48:Y48"/>
+    <mergeCell ref="O7:T7"/>
+    <mergeCell ref="AM16:AR16"/>
+    <mergeCell ref="AA17:AF17"/>
+    <mergeCell ref="AM17:AR17"/>
+    <mergeCell ref="AD6:AW6"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="C19:AX19"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="AA16:AF16"/>
+    <mergeCell ref="AG17:AL17"/>
+    <mergeCell ref="I17:Z17"/>
+    <mergeCell ref="AG7:AL7"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="AS17:AW17"/>
     <mergeCell ref="AM50:AR50"/>
     <mergeCell ref="K50:Y50"/>
     <mergeCell ref="C43:Q43"/>
@@ -2624,33 +2643,6 @@
     <mergeCell ref="Z50:AF50"/>
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="C19:AX19"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="AA16:AF16"/>
-    <mergeCell ref="AG17:AL17"/>
-    <mergeCell ref="I17:Z17"/>
-    <mergeCell ref="AG7:AL7"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="AS17:AW17"/>
-    <mergeCell ref="C52:AW52"/>
-    <mergeCell ref="F57:AT57"/>
-    <mergeCell ref="S2:U2"/>
-    <mergeCell ref="AS7:AW7"/>
-    <mergeCell ref="AS16:AW16"/>
-    <mergeCell ref="AM48:AR48"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="I16:Z16"/>
-    <mergeCell ref="I6:AC6"/>
-    <mergeCell ref="K48:Y48"/>
-    <mergeCell ref="O7:T7"/>
-    <mergeCell ref="AM16:AR16"/>
-    <mergeCell ref="AA17:AF17"/>
-    <mergeCell ref="AM17:AR17"/>
-    <mergeCell ref="AD6:AW6"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
